--- a/RegisterData.xlsx
+++ b/RegisterData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationOpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0D96FF-534D-4972-953F-36D7D8258BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0471D103-F173-4155-9645-A479F4CDAB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="46">
   <si>
     <t>TestType</t>
   </si>
@@ -49,155 +49,133 @@
     <t>HAPPY</t>
   </si>
   <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>alice01@mail.com</t>
-  </si>
-  <si>
-    <t>1234567</t>
-  </si>
-  <si>
-    <t>Pass1234</t>
-  </si>
-  <si>
-    <t>Your account has been created!</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t>bob.johnson@example.com</t>
-  </si>
-  <si>
-    <t>987654321</t>
-  </si>
-  <si>
-    <t>Secure!9</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>carol.lee2023@mail.net</t>
-  </si>
-  <si>
-    <t>5551234</t>
-  </si>
-  <si>
-    <t>MyPass2023</t>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Wick</t>
+  </si>
+  <si>
+    <t>0901234567</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>SUCCESS</t>
+  </si>
+  <si>
+    <t>BOUNDARY_FAIL</t>
+  </si>
+  <si>
+    <t>john03@mail.com</t>
+  </si>
+  <si>
+    <t>First Name must be between 1 and 32 characters!</t>
+  </si>
+  <si>
+    <t>aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa</t>
+  </si>
+  <si>
+    <t>john04@mail.com</t>
   </si>
   <si>
     <t>NEGATIVE</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>john068@mail.com</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>NewPass1</t>
+    <t>E-Mail Address does not appear to be valid!</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Telephone must be between 3 and 32 characters!</t>
+  </si>
+  <si>
+    <t>Nhung</t>
+  </si>
+  <si>
+    <t>Nguyen</t>
+  </si>
+  <si>
+    <t>123457</t>
+  </si>
+  <si>
+    <t>0901234568</t>
+  </si>
+  <si>
+    <t>0901234570</t>
+  </si>
+  <si>
+    <t>123455</t>
+  </si>
+  <si>
+    <t>13579</t>
+  </si>
+  <si>
+    <t>Vinh</t>
+  </si>
+  <si>
+    <t>john@schsvl.com</t>
+  </si>
+  <si>
+    <t>scsjnskvls</t>
+  </si>
+  <si>
+    <t>Wichsb@gmail.com</t>
+  </si>
+  <si>
+    <t>john6546@mail.com</t>
+  </si>
+  <si>
+    <t>johna@mail.com</t>
+  </si>
+  <si>
+    <t>john72@mail.com</t>
   </si>
   <si>
     <t>Warning: E-Mail Address is already registered!</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>david.brown@example.com</t>
-  </si>
-  <si>
-    <t>321654</t>
-  </si>
-  <si>
-    <t>Password1</t>
-  </si>
-  <si>
-    <t>Password2</t>
+    <t>123vsv</t>
+  </si>
+  <si>
+    <t>123ert</t>
+  </si>
+  <si>
+    <t>hanh@gmail.com</t>
+  </si>
+  <si>
+    <t>123e</t>
   </si>
   <si>
     <t>Password confirmation does not match password!</t>
   </si>
   <si>
-    <t>Eve</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>eve.white@example.com</t>
-  </si>
-  <si>
-    <t>12A45</t>
-  </si>
-  <si>
-    <t>EvePass123</t>
-  </si>
-  <si>
-    <t>Telephone must be between 3 and 32 characters!</t>
-  </si>
-  <si>
-    <t>BOUNDARY</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>Boundary</t>
-  </si>
-  <si>
-    <t>z.boundary@mail.com</t>
-  </si>
-  <si>
-    <t>12345</t>
-  </si>
-  <si>
-    <t>BoundPass1</t>
-  </si>
-  <si>
-    <t>Mike</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>mike.short@mail.com</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>ShortPass1</t>
+    <t>Velvet</t>
+  </si>
+  <si>
+    <t>Password must be between 6 and 32 characters!</t>
+  </si>
+  <si>
+    <t>arh1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -220,13 +198,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -527,14 +509,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -568,210 +549,242 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
       <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
+        <v>27</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" t="s">
-        <v>49</v>
+        <v>10</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
+        <v>10</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9A3B68BD-EFE0-4905-AB37-879F3D9C9190}"/>
+    <hyperlink ref="D7" r:id="rId2" xr:uid="{6A641D9E-0927-46DF-A1CD-8A99F38B3FC6}"/>
+    <hyperlink ref="D9" r:id="rId3" xr:uid="{7B8D309D-538D-43B0-81C5-9978AC1AE4BB}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{E19C5525-EF9D-4F94-800D-FBB22744D2B9}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{9B9FF1AA-74F4-4405-965D-26EC5800FFE6}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{007E8EB1-7785-49A5-A74E-48EEB93CD05D}"/>
+    <hyperlink ref="D10" r:id="rId7" xr:uid="{8E7FADD6-8AE1-4D01-9A5F-5C99F9C70AE2}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/RegisterData.xlsx
+++ b/RegisterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationOpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0471D103-F173-4155-9645-A479F4CDAB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAE6E38-5FAA-415A-95BF-01834BD5874F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/RegisterData.xlsx
+++ b/RegisterData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationOpenCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D770BCE-D8B5-4F0B-A985-A997912EBFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA98D2AC-8D3A-4CCE-9B10-0FE128D49C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4872" yWindow="3360" windowWidth="10320" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,9 +115,6 @@
     <t>Vinh</t>
   </si>
   <si>
-    <t>john@schsvl.com</t>
-  </si>
-  <si>
     <t>scsjnskvls</t>
   </si>
   <si>
@@ -158,6 +155,9 @@
   </si>
   <si>
     <t>arh1</t>
+  </si>
+  <si>
+    <t>john@</t>
   </si>
 </sst>
 </file>
@@ -555,12 +555,12 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -575,7 +575,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -587,13 +587,13 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -633,7 +633,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>21</v>
@@ -682,7 +682,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -694,7 +694,7 @@
         <v>29</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -708,16 +708,16 @@
         <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -734,16 +734,16 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
         <v>20</v>
@@ -760,19 +760,19 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
         <v>41</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
